--- a/output/tripakarta/Final_Tripakarta_2024_WA_QSSPL.xlsx
+++ b/output/tripakarta/Final_Tripakarta_2024_WA_QSSPL.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,10 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -35,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -43,12 +47,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,37 +437,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Reinsured</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Type_COB</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Provision_Commission</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Bottom_LR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Upper_LR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RI_Commission</t>
         </is>
@@ -668,42 +687,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cedant</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>COB</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Deficit_Clause_Year</t>
         </is>
